--- a/output/07_Aviat_Ceragon_구성가격비교.xlsx
+++ b/output/07_Aviat_Ceragon_구성가격비교.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>47710885.87799999</v>
+        <v>47680619.87799999</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>35608005.346</v>
+        <v>35592123.746</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>47709791.64199999</v>
+        <v>47679525.64199999</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>35608005.346</v>
+        <v>35592123.746</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>65924718.83999998</v>
+        <v>65872577.23999999</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>55704470.07800001</v>
+        <v>55681097.27800001</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>65922530.36799998</v>
+        <v>65870388.76799998</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>55702281.60600001</v>
+        <v>55678908.80600001</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>83890988.12600002</v>
+        <v>83816970.92600001</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>75626915.888</v>
+        <v>75596051.888</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>83887705.41800003</v>
+        <v>83813688.21800002</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>75623633.18000001</v>
+        <v>75592769.18000001</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>103910327.142</v>
+        <v>103814434.342</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>91513678.52200001</v>
+        <v>91475323.32200001</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>103905950.198</v>
+        <v>103810057.398</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>91509301.57800001</v>
+        <v>91470946.37800001</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
